--- a/artfynd/A 48609-2025 artfynd.xlsx
+++ b/artfynd/A 48609-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -902,6 +902,449 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/55545370</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137452961</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96304</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1131</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Asphättemossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Nyholmiella gymnostoma</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Bruch ex Brid.) Holmen &amp; Warncke</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Grönlundsmur N, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>591261</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6701457</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>klibbalkärr</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137452961</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137452962</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96542</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Grönlundsmur N, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>591260</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6701458</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>klibbalkärr</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137452962</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137452960</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96649</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Grönlundsmur N, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>591241</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6701399</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>klibbalkärr</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137452960</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137452959</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96769</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Grönlundsmur N, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>591224</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6701384</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>klibbalkärr</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>alsockel</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137452959</t>
         </is>
       </c>
     </row>
@@ -909,6 +1352,10 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48609-2025 artfynd.xlsx
+++ b/artfynd/A 48609-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>137452961</v>
       </c>
       <c r="B4" t="n">
-        <v>96304</v>
+        <v>96308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>137452962</v>
       </c>
       <c r="B5" t="n">
-        <v>96542</v>
+        <v>96546</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>137452960</v>
       </c>
       <c r="B6" t="n">
-        <v>96649</v>
+        <v>96653</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>137452959</v>
       </c>
       <c r="B7" t="n">
-        <v>96769</v>
+        <v>96773</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
